--- a/results/link-prediction-gcn/Link/1shot/PROTEINS/GCN_total_results.xlsx
+++ b/results/link-prediction-gcn/Link/1shot/PROTEINS/GCN_total_results.xlsx
@@ -893,457 +893,457 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.4852±0.0000</t>
+          <t>0.4854±0.0000</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.5150±0.0000</t>
+          <t>0.5189±0.0052</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.5149±0.0000</t>
+          <t>0.5146±0.0000</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.5148±0.0000</t>
+          <t>0.5144±0.0004</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.5155±0.0000</t>
+          <t>0.5150±0.0009</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.5147±0.0000</t>
+          <t>0.5257±0.0094</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.5150±0.0000</t>
+          <t>0.5146±0.0010</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.5147±0.0000</t>
+          <t>0.5142±0.0001</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.5147±0.0000</t>
+          <t>0.5142±0.0001</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.5147±0.0000</t>
+          <t>0.5142±0.0001</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.5148±0.0000</t>
+          <t>0.5145±0.0004</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.5397±0.0000</t>
+          <t>0.5375±0.0161</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.5147±0.0000</t>
+          <t>0.5269±0.0111</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.4852±0.0000</t>
+          <t>0.4854±0.0000</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.5198±0.0000</t>
+          <t>0.5229±0.0059</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.5151±0.0000</t>
+          <t>0.5209±0.0088</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.5259±0.0000</t>
+          <t>0.5127±0.0023</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.5163±0.0000</t>
+          <t>0.5150±0.0010</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.5152±0.0000</t>
+          <t>0.5176±0.0042</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.5154±0.0000</t>
+          <t>0.5217±0.0094</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.5154±0.0000</t>
+          <t>0.5170±0.0027</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.5154±0.0000</t>
+          <t>0.5170±0.0027</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.5154±0.0000</t>
+          <t>0.5170±0.0027</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.5206±0.0000</t>
+          <t>0.5144±0.0002</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.5148±0.0000</t>
+          <t>0.5146±0.0000</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.5154±0.0000</t>
+          <t>0.5136±0.0016</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.4852±0.0000</t>
+          <t>0.4834±0.0027</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.5137±0.0000</t>
+          <t>0.5146±0.0003</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.5152±0.0000</t>
+          <t>0.5148±0.0002</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0.5147±0.0000</t>
+          <t>0.5325±0.0138</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.5261±0.0000</t>
+          <t>0.5199±0.0031</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.5242±0.0000</t>
+          <t>0.5405±0.0203</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
+          <t>0.5151±0.0005</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.5331±0.0076</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.5331±0.0076</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.5331±0.0076</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0.5146±0.0003</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0.5462±0.0026</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0.5209±0.0077</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0.4854±0.0001</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.5227±0.0087</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.5178±0.0066</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.5326±0.0040</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.5453±0.0074</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0.5228±0.0064</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.5289±0.0030</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.5535±0.0057</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.5535±0.0057</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>0.5535±0.0057</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0.5335±0.0034</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.5233±0.0111</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.5402±0.0109</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>0.4854±0.0000</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>0.5187±0.0029</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.5154±0.0010</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.5221±0.0109</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>0.5202±0.0041</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>0.5151±0.0012</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0.5150±0.0009</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>0.5161±0.0025</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>0.5161±0.0025</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>0.5161±0.0025</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.5169±0.0019</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.5192±0.0053</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>0.5237±0.0132</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>0.4854±0.0000</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>0.5196±0.0069</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
           <t>0.5146±0.0000</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0.5224±0.0000</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>0.5224±0.0000</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0.5224±0.0000</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>0.5147±0.0000</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>0.5553±0.0000</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>0.5267±0.0000</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0.4852±0.0000</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0.5525±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.5151±0.0000</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.5210±0.0000</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>0.5401±0.0000</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>0.5327±0.0000</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>0.5484±0.0000</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>0.5525±0.0000</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>0.5525±0.0000</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>0.5525±0.0000</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>0.5569±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0.5365±0.0000</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>0.5490±0.0000</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>0.4852±0.0000</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>0.5147±0.0000</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0.5148±0.0000</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0.5148±0.0000</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>0.5148±0.0000</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>0.5148±0.0000</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>0.5145±0.0000</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>0.5148±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>0.5148±0.0000</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>0.5148±0.0000</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.5149±0.0000</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0.5121±0.0000</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>0.5146±0.0000</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>0.4852±0.0000</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>0.5149±0.0000</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>0.5148±0.0000</t>
-        </is>
-      </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.5148±0.0000</t>
+          <t>0.5144±0.0005</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.5148±0.0000</t>
+          <t>0.5155±0.0006</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.5145±0.0000</t>
+          <t>0.5201±0.0036</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.5149±0.0000</t>
+          <t>0.5167±0.0032</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>0.5145±0.0000</t>
+          <t>0.5169±0.0029</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>0.5145±0.0000</t>
+          <t>0.5169±0.0029</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>0.5145±0.0000</t>
+          <t>0.5169±0.0029</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>0.5149±0.0000</t>
+          <t>0.5180±0.0038</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>0.5156±0.0000</t>
+          <t>0.5299±0.0106</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>0.5144±0.0000</t>
+          <t>0.5184±0.0031</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>0.4852±0.0000</t>
+          <t>0.4854±0.0000</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0.5159±0.0000</t>
+          <t>0.5186±0.0006</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0.5219±0.0000</t>
+          <t>0.5301±0.0183</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.5220±0.0000</t>
+          <t>0.5279±0.0104</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.5244±0.0000</t>
+          <t>0.5209±0.0021</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.5154±0.0000</t>
+          <t>0.5158±0.0022</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.5266±0.0000</t>
+          <t>0.5209±0.0043</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.5160±0.0000</t>
+          <t>0.5215±0.0091</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.5160±0.0000</t>
+          <t>0.5215±0.0091</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.5160±0.0000</t>
+          <t>0.5215±0.0091</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>0.5207±0.0000</t>
+          <t>0.5199±0.0039</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>0.5358±0.0000</t>
+          <t>0.5269±0.0173</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>0.5154±0.0000</t>
+          <t>0.5170±0.0029</t>
         </is>
       </c>
     </row>
@@ -1360,452 +1360,452 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.6796±0.0000</t>
+          <t>0.6767±0.0016</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.6797±0.0000</t>
+          <t>0.6795±0.0001</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.6797±0.0000</t>
+          <t>0.6782±0.0019</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>0.6788±0.0003</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.6774±0.0025</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.6784±0.0006</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.6790±0.0001</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.6790±0.0001</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.6790±0.0001</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.6791±0.0003</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.6509±0.0204</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.6775±0.0016</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0.6802±0.0008</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0.6773±0.0032</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.6522±0.0200</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.6781±0.0003</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0.6792±0.0003</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0.6787±0.0008</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.6788±0.0005</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.6788±0.0005</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.6788±0.0005</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.6793±0.0002</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>0.6795±0.0000</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0.6795±0.0000</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.6796±0.0000</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.6795±0.0000</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.6795±0.0000</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.6795±0.0000</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0.6797±0.0000</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0.6642±0.0000</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0.6794±0.0000</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.6777±0.0023</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0.0060±0.0067</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0.6794±0.0002</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0.6790±0.0003</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0.6818±0.0019</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0.6771±0.0021</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0.6760±0.0030</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.6782±0.0003</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.6736±0.0025</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.6736±0.0025</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.6736±0.0025</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>0.6791±0.0002</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.6685±0.0023</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.6757±0.0030</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0.0009±0.0001</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.6734±0.0079</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.6779±0.0017</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.6765±0.0058</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.6761±0.0052</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.6779±0.0020</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.6730±0.0047</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.6731±0.0059</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.6731±0.0059</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0.6731±0.0059</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.6750±0.0050</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.6719±0.0085</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.6713±0.0069</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0.6795±0.0000</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0.6797±0.0000</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0.6788±0.0000</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0.6788±0.0000</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>0.6798±0.0000</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>0.6795±0.0000</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0.6794±0.0000</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0.6794±0.0000</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.6794±0.0000</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0.6801±0.0000</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.6797±0.0000</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>0.6799±0.0000</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>0.6794±0.0005</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.6794±0.0002</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.6755±0.0018</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.6769±0.0019</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>0.6762±0.0029</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>0.6791±0.0002</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.6789±0.0006</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.6789±0.0006</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.6789±0.0006</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.6789±0.0001</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.6732±0.0052</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>0.6706±0.0111</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>0.6773±0.0000</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>0.6798±0.0000</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>0.6796±0.0000</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0.6807±0.0000</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0.6773±0.0000</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0.6794±0.0000</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0.6763±0.0000</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>0.6763±0.0000</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>0.6763±0.0000</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>0.6794±0.0000</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>0.6679±0.0000</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>0.6687±0.0000</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>0.6770±0.0032</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0.6794±0.0001</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>0.6792±0.0006</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>0.6784±0.0009</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>0.6762±0.0021</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>0.6794±0.0001</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>0.6796±0.0003</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>0.6796±0.0003</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>0.6796±0.0003</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>0.6787±0.0008</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>0.6678±0.0089</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>0.6785±0.0016</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>0.6725±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.6797±0.0000</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.6724±0.0000</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>0.6807±0.0000</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>0.6749±0.0000</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>0.6733±0.0000</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>0.6737±0.0000</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>0.6737±0.0000</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>0.6737±0.0000</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>0.6702±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.6767±0.0000</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>0.6696±0.0000</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>0.0000±0.0000</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>0.6795±0.0000</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0.6797±0.0000</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0.6797±0.0000</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>0.6795±0.0000</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>0.6795±0.0000</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>0.6792±0.0000</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>0.6795±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>0.6795±0.0000</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>0.6795±0.0000</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.6795±0.0000</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0.6759±0.0000</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>0.6794±0.0000</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>0.0000±0.0000</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>0.6795±0.0000</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>0.6797±0.0000</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>0.6797±0.0000</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>0.6795±0.0000</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>0.6792±0.0000</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>0.6796±0.0000</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>0.6792±0.0000</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>0.6792±0.0000</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>0.6792±0.0000</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>0.6795±0.0000</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>0.6696±0.0000</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>0.6792±0.0000</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>0.0000±0.0000</t>
-        </is>
-      </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>0.6739±0.0000</t>
+          <t>0.6729±0.0024</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0.6784±0.0000</t>
+          <t>0.6728±0.0031</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.6784±0.0000</t>
+          <t>0.6718±0.0047</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.6732±0.0000</t>
+          <t>0.6780±0.0004</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0.6788±0.0000</t>
+          <t>0.6791±0.0006</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.6728±0.0000</t>
+          <t>0.6777±0.0025</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.6742±0.0000</t>
+          <t>0.6773±0.0016</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.6742±0.0000</t>
+          <t>0.6773±0.0016</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.6742±0.0000</t>
+          <t>0.6773±0.0016</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>0.6761±0.0000</t>
+          <t>0.6744±0.0024</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>0.6670±0.0000</t>
+          <t>0.6685±0.0157</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>0.6726±0.0000</t>
+          <t>0.6777±0.0002</t>
         </is>
       </c>
     </row>
@@ -1817,457 +1817,457 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.4271±0.0000</t>
+          <t>0.6372±0.0210</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.4528±0.0000</t>
+          <t>0.5934±0.0183</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.4998±0.0000</t>
+          <t>0.5000±0.0001</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.5001±0.0000</t>
+          <t>0.5437±0.0623</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.5811±0.0000</t>
+          <t>0.5933±0.0123</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.4999±0.0000</t>
+          <t>0.6048±0.0564</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.4459±0.0000</t>
+          <t>0.5844±0.0365</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.4998±0.0000</t>
+          <t>0.6240±0.0172</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.4998±0.0000</t>
+          <t>0.6240±0.0172</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.4998±0.0000</t>
+          <t>0.6240±0.0172</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.4491±0.0000</t>
+          <t>0.5367±0.0115</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.5633±0.0000</t>
+          <t>0.5594±0.0031</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>0.5791±0.0274</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0.4212±0.0398</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0.5693±0.0286</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0.5079±0.0113</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0.5457±0.0342</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0.5585±0.0139</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0.5579±0.0261</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>0.5691±0.0080</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.5701±0.0097</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.5701±0.0097</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.5701±0.0097</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.5185±0.0051</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0.6017±0.0036</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>0.5827±0.0290</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>0.5492±0.0725</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>0.4935±0.0300</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>0.5005±0.0004</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>0.5626±0.0257</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0.5471±0.0367</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0.5630±0.0198</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0.5245±0.0238</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0.5388±0.0274</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0.5388±0.0274</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>0.5388±0.0275</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>0.4985±0.0012</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>0.5750±0.0022</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>0.5517±0.0122</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>0.4713±0.0847</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>0.5229±0.0205</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.5117±0.0203</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.5425±0.0168</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.5685±0.0283</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>0.5697±0.0392</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>0.5046±0.0058</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>0.5741±0.0143</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>0.5741±0.0143</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>0.5741±0.0143</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>0.5306±0.0312</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>0.5495±0.0027</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>0.5678±0.0008</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>0.6412±0.0107</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>0.6064±0.0155</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0.5357±0.0506</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0.5830±0.0450</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>0.6144±0.0306</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>0.6415±0.0074</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>0.6206±0.0276</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>0.6214±0.0161</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>0.6214±0.0161</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>0.6214±0.0161</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>0.5374±0.0278</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>0.5599±0.0014</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>0.5692±0.0314</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>0.6388±0.0133</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>0.5589±0.0485</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0.3883±0.0000</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0.5127±0.0000</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0.5003±0.0000</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0.5036±0.0000</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0.5421±0.0000</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>0.5693±0.0000</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>0.4773±0.0000</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0.5462±0.0000</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0.5462±0.0000</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0.5462±0.0000</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0.5320±0.0000</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0.6123±0.0000</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>0.5338±0.0000</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>0.4996±0.0000</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>0.4849±0.0000</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>0.5004±0.0000</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>0.4999±0.0000</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0.5126±0.0000</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0.5114±0.0000</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0.4733±0.0000</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0.5096±0.0000</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>0.5096±0.0000</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>0.5096±0.0000</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>0.4992±0.0000</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>0.5858±0.0000</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>0.5181±0.0000</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>0.4995±0.0000</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>0.5480±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>0.5003±0.0000</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.5077±0.0000</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>0.5350±0.0000</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>0.5337±0.0000</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>0.5385±0.0000</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>0.5446±0.0000</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>0.5446±0.0000</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>0.5446±0.0000</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>0.5475±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>0.5954±0.0000</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>0.5412±0.0000</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>0.6172±0.0000</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>0.4843±0.0000</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0.4999±0.0000</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>0.4989±0.0000</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>0.4998±0.0000</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>0.4997±0.0000</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>0.4568±0.0000</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>0.4996±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>0.4996±0.0000</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>0.4996±0.0000</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>0.4548±0.0000</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>0.5596±0.0000</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>0.4991±0.0000</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>0.6129±0.0000</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>0.4485±0.0000</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>0.5311±0.0437</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>0.5910±0.0117</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>0.6280±0.0242</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>0.5742±0.0435</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>0.5388±0.0359</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>0.5388±0.0359</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>0.5388±0.0359</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>0.5549±0.0296</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>0.5610±0.0045</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>0.5993±0.0329</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>0.5206±0.0000</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>0.4513±0.0000</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>0.5271±0.0000</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>0.5271±0.0000</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>0.5271±0.0000</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>0.4431±0.0000</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>0.5582±0.0000</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
-        <is>
-          <t>0.5268±0.0000</t>
-        </is>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>0.5004±0.0000</t>
-        </is>
-      </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.5580±0.0000</t>
+          <t>0.6171±0.0341</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.5079±0.0000</t>
+          <t>0.5426±0.0254</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.5092±0.0000</t>
+          <t>0.5565±0.0442</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.5224±0.0000</t>
+          <t>0.5913±0.0078</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.5704±0.0000</t>
+          <t>0.6223±0.0245</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.5396±0.0000</t>
+          <t>0.5921±0.0269</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.5555±0.0000</t>
+          <t>0.5905±0.0190</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.5555±0.0000</t>
+          <t>0.5905±0.0190</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.5555±0.0000</t>
+          <t>0.5905±0.0190</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>0.5309±0.0000</t>
+          <t>0.5805±0.0301</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>0.5688±0.0000</t>
+          <t>0.5680±0.0009</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>0.5660±0.0000</t>
+          <t>0.5771±0.0066</t>
         </is>
       </c>
     </row>
@@ -2279,457 +2279,457 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.4518±0.0000</t>
+          <t>0.6473±0.0213</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.4827±0.0000</t>
+          <t>0.5724±0.0121</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.5147±0.0000</t>
+          <t>0.5146±0.0000</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.5148±0.0000</t>
+          <t>0.5603±0.0649</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.5583±0.0000</t>
+          <t>0.5754±0.0174</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.5148±0.0000</t>
+          <t>0.5941±0.0592</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.4792±0.0000</t>
+          <t>0.5601±0.0274</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.5147±0.0000</t>
+          <t>0.6158±0.0327</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.5147±0.0000</t>
+          <t>0.6158±0.0327</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.5147±0.0000</t>
+          <t>0.6158±0.0327</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.4791±0.0000</t>
+          <t>0.5279±0.0085</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.5595±0.0000</t>
+          <t>0.5543±0.0026</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.5148±0.0000</t>
+          <t>0.5595±0.0311</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.4341±0.0000</t>
+          <t>0.4542±0.0250</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.5158±0.0000</t>
+          <t>0.5556±0.0142</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.5150±0.0000</t>
+          <t>0.5187±0.0060</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.5103±0.0000</t>
+          <t>0.5689±0.0408</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.5403±0.0000</t>
+          <t>0.5584±0.0155</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.5535±0.0000</t>
+          <t>0.5530±0.0136</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.4956±0.0000</t>
+          <t>0.5525±0.0030</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.5475±0.0000</t>
+          <t>0.5692±0.0097</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5475±0.0000</t>
+          <t>0.5692±0.0097</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.5475±0.0000</t>
+          <t>0.5692±0.0097</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.5284±0.0000</t>
+          <t>0.5286±0.0066</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.5916±0.0000</t>
+          <t>0.5807±0.0027</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.5314±0.0000</t>
+          <t>0.5752±0.0211</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.5148±0.0000</t>
+          <t>0.5354±0.0487</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.5011±0.0000</t>
+          <t>0.5046±0.0198</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.5150±0.0000</t>
+          <t>0.5148±0.0002</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.5148±0.0000</t>
+          <t>0.5600±0.0171</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.5212±0.0000</t>
+          <t>0.5388±0.0233</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.5206±0.0000</t>
+          <t>0.5597±0.0210</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.5006±0.0000</t>
+          <t>0.5283±0.0126</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.5197±0.0000</t>
+          <t>0.5384±0.0190</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.5197±0.0000</t>
+          <t>0.5384±0.0190</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.5197±0.0000</t>
+          <t>0.5384±0.0190</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.5144±0.0000</t>
+          <t>0.5138±0.0006</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.5780±0.0000</t>
+          <t>0.5652±0.0007</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.5257±0.0000</t>
+          <t>0.5549±0.0101</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.5147±0.0000</t>
+          <t>0.4904±0.0497</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.5333±0.0000</t>
+          <t>0.5194±0.0147</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.5149±0.0000</t>
+          <t>0.5215±0.0116</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.5187±0.0000</t>
+          <t>0.5361±0.0098</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.5335±0.0000</t>
+          <t>0.5517±0.0175</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.5320±0.0000</t>
+          <t>0.5560±0.0362</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.5232±0.0000</t>
+          <t>0.5039±0.0046</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.5387±0.0000</t>
+          <t>0.5654±0.0146</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.5387±0.0000</t>
+          <t>0.5654±0.0146</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.5387±0.0000</t>
+          <t>0.5654±0.0146</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.5354±0.0000</t>
+          <t>0.5269±0.0219</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.5829±0.0000</t>
+          <t>0.5412±0.0027</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.5369±0.0000</t>
+          <t>0.5590±0.0023</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.6264±0.0000</t>
+          <t>0.6501±0.0094</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.4892±0.0000</t>
+          <t>0.5843±0.0192</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.5148±0.0000</t>
+          <t>0.5381±0.0333</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.5143±0.0000</t>
+          <t>0.5952±0.0494</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.5147±0.0000</t>
+          <t>0.6061±0.0418</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
+          <t>0.6359±0.0118</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>0.5989±0.0284</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>0.6043±0.0193</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>0.6043±0.0193</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>0.6043±0.0193</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>0.5244±0.0161</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0.5528±0.0011</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>0.5513±0.0245</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>0.6468±0.0126</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>0.5434±0.0352</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>0.5146±0.0001</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>0.5483±0.0475</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>0.5658±0.0186</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>0.6152±0.0310</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>0.5586±0.0372</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>0.5342±0.0165</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>0.5342±0.0165</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>0.5342±0.0165</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>0.5404±0.0206</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>0.5569±0.0022</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>0.5827±0.0291</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
           <t>0.5146±0.0000</t>
         </is>
       </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>0.4842±0.0000</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>0.5146±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>0.5146±0.0000</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>0.5146±0.0000</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>0.4820±0.0000</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0.5560±0.0000</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>0.5144±0.0000</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>0.6217±0.0000</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>0.4784±0.0000</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>0.5148±0.0000</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>0.5148±0.0000</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>0.5148±0.0000</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>0.5127±0.0000</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>0.4809±0.0000</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>0.5151±0.0000</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>0.5151±0.0000</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>0.5151±0.0000</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>0.4750±0.0000</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>0.5546±0.0000</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr">
-        <is>
-          <t>0.5197±0.0000</t>
-        </is>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>0.5153±0.0000</t>
-        </is>
-      </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.5538±0.0000</t>
+          <t>0.6050±0.0293</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5465±0.0247</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.5195±0.0000</t>
+          <t>0.5603±0.0457</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.5269±0.0000</t>
+          <t>0.5675±0.0049</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.5538±0.0000</t>
+          <t>0.6052±0.0203</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.5394±0.0000</t>
+          <t>0.5784±0.0286</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.5412±0.0000</t>
+          <t>0.5773±0.0238</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.5412±0.0000</t>
+          <t>0.5773±0.0238</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.5412±0.0000</t>
+          <t>0.5773±0.0238</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>0.5382±0.0000</t>
+          <t>0.5688±0.0190</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>0.5637±0.0000</t>
+          <t>0.5575±0.0007</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>0.5528±0.0000</t>
+          <t>0.5638±0.0097</t>
         </is>
       </c>
     </row>
